--- a/output/pdf_financials_xlsx/ROS.xlsx
+++ b/output/pdf_financials_xlsx/ROS.xlsx
@@ -1261,40 +1261,40 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.387063</v>
+        <v>-0.387063</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.491431</v>
+        <v>-0.491431</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.14568</v>
+        <v>-0.14568</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.573147</v>
+        <v>-0.573147</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.101625</v>
+        <v>-0.101625</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.08756799999999999</v>
+        <v>-0.08756799999999999</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.107318</v>
+        <v>-0.107318</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.079309</v>
+        <v>-0.079309</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.090401</v>
+        <v>-0.090401</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-0.513518</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1.604575</v>
+        <v>-1.604575</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>5.711658</v>
+        <v>-5.711658</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>-24.62322</v>
@@ -1561,40 +1561,40 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.387063</v>
+        <v>-0.387063</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.491431</v>
+        <v>-0.491431</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.14568</v>
+        <v>-0.14568</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.573147</v>
+        <v>-0.573147</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.101625</v>
+        <v>-0.101625</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.08756799999999999</v>
+        <v>-0.08756799999999999</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.107318</v>
+        <v>-0.107318</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.079309</v>
+        <v>-0.079309</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.090401</v>
+        <v>-0.090401</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-0.513518</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>1.604575</v>
+        <v>-1.604575</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>5.711658</v>
+        <v>-5.711658</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>-24.62322</v>
@@ -1735,40 +1735,40 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.387063</v>
+        <v>-0.387063</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.491431</v>
+        <v>-0.491431</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.14568</v>
+        <v>-0.14568</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.573147</v>
+        <v>-0.573147</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.101625</v>
+        <v>-0.101625</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.08756799999999999</v>
+        <v>-0.08756799999999999</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.107318</v>
+        <v>-0.107318</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.079309</v>
+        <v>-0.079309</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.090401</v>
+        <v>-0.090401</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-0.513518</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>1.604575</v>
+        <v>-1.604575</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>5.711658</v>
+        <v>-5.711658</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>-24.62322</v>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>27.647357</v>
+        <v>-27.647357</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>27.301722</v>
+        <v>-27.301722</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>27.292714</v>
+        <v>-27.292714</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1955,10 +1955,10 @@
         <v>39.501385</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-57.30625</v>
+        <v>57.30625</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-107.767132</v>
+        <v>107.767132</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -1989,40 +1989,40 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.387063</v>
+        <v>-0.387063</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.491431</v>
+        <v>-0.491431</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.14568</v>
+        <v>-0.14568</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.573147</v>
+        <v>-0.573147</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.101625</v>
+        <v>-0.101625</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.08756799999999999</v>
+        <v>-0.08756799999999999</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.107318</v>
+        <v>-0.107318</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.079309</v>
+        <v>-0.079309</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.090401</v>
+        <v>-0.090401</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-0.513518</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1.604575</v>
+        <v>-1.604575</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>5.711658</v>
+        <v>-5.711658</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-24.62322</v>
@@ -2105,40 +2105,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.387063</v>
+        <v>-0.387063</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.491431</v>
+        <v>-0.491431</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.14568</v>
+        <v>-0.14568</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.573147</v>
+        <v>-0.573147</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.101625</v>
+        <v>-0.101625</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.08756799999999999</v>
+        <v>-0.08756799999999999</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.107318</v>
+        <v>-0.107318</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.079309</v>
+        <v>-0.079309</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.090401</v>
+        <v>-0.090401</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-0.513518</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.604575</v>
+        <v>-1.604575</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>5.711658</v>
+        <v>-5.711658</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-24.62322</v>
@@ -2255,40 +2255,40 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0</v>
@@ -28483,25 +28483,25 @@
         </is>
       </c>
       <c r="J199" s="5" t="n">
-        <v>0.08756799999999999</v>
+        <v>-0.08756799999999999</v>
       </c>
       <c r="K199" s="5" t="n">
-        <v>0.107318</v>
+        <v>-0.107318</v>
       </c>
       <c r="L199" s="5" t="n">
-        <v>0.079309</v>
+        <v>-0.079309</v>
       </c>
       <c r="M199" s="5" t="n">
-        <v>0.090401</v>
+        <v>-0.090401</v>
       </c>
       <c r="N199" s="5" t="n">
         <v>-0.513518</v>
       </c>
       <c r="O199" s="5" t="n">
-        <v>1.604575</v>
+        <v>-1.604575</v>
       </c>
       <c r="P199" s="5" t="n">
-        <v>5.711658</v>
+        <v>-5.711658</v>
       </c>
       <c r="Q199" s="5" t="n">
         <v>-24.62322</v>
@@ -31346,13 +31346,13 @@
         </is>
       </c>
       <c r="H228" s="5" t="n">
-        <v>0.573147</v>
+        <v>-0.573147</v>
       </c>
       <c r="I228" s="5" t="n">
-        <v>0.101625</v>
+        <v>-0.101625</v>
       </c>
       <c r="J228" s="5" t="n">
-        <v>0.08756799999999999</v>
+        <v>-0.08756799999999999</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
@@ -34131,16 +34131,16 @@
         </is>
       </c>
       <c r="E256" s="5" t="n">
-        <v>0.387063</v>
+        <v>-0.387063</v>
       </c>
       <c r="F256" s="5" t="n">
-        <v>0.491431</v>
+        <v>-0.491431</v>
       </c>
       <c r="G256" s="5" t="n">
-        <v>0.14568</v>
+        <v>-0.14568</v>
       </c>
       <c r="H256" s="5" t="n">
-        <v>0.573147</v>
+        <v>-0.573147</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ROS.xlsx
+++ b/output/pdf_financials_xlsx/ROS.xlsx
@@ -922,7 +922,7 @@
         <v>0.053802</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.054384</v>
+        <v>0.57385</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0.101625</v>
@@ -1029,16 +1029,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.039887</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008481000000000001</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002779</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000703</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1062,13 +1062,13 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.013841</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.007892</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.006291</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0</v>
@@ -1989,16 +1989,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.387063</v>
+        <v>-0.347176</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.491431</v>
+        <v>-0.48295</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.14568</v>
+        <v>-0.142901</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.573147</v>
+        <v>-0.57385</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.101625</v>
@@ -2022,13 +2022,13 @@
         <v>-1.604575</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-5.711658</v>
+        <v>-5.725499</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-24.62322</v>
+        <v>-24.631112</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-16.782371</v>
+        <v>-16.788662</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-4.872103</v>
@@ -2105,16 +2105,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.387063</v>
+        <v>-0.347176</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.491431</v>
+        <v>-0.48295</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.14568</v>
+        <v>-0.142901</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.573147</v>
+        <v>-0.57385</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.101625</v>
@@ -2138,13 +2138,13 @@
         <v>-1.604575</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-5.711658</v>
+        <v>-5.725499</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-24.62322</v>
+        <v>-24.631112</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-16.782371</v>
+        <v>-16.788662</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-4.872103</v>
@@ -2429,40 +2429,40 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.033991</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.003214</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.003917</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.002269</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.018181</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.05078</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.240219</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>6.867764</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.046953</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.01878</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>1.281773</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.526822</v>
       </c>
     </row>
     <row r="35">
@@ -2549,40 +2549,40 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.033991</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.003214</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.003917</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.002269</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.018181</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.05078</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.240219</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>6.867764</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.046953</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.01878</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>1.281773</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.526822</v>
       </c>
     </row>
     <row r="37">
@@ -3269,40 +3269,40 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.034824</v>
+        <v>0.000833</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.004047</v>
+        <v>0.000833</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.00475</v>
+        <v>0.000833</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.003102</v>
+        <v>0.000833</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.018181</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.188378</v>
+        <v>0.137598</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.326268</v>
+        <v>0.086049</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>7.079591</v>
+        <v>0.211827</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.103841</v>
+        <v>0.056888</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.120778</v>
+        <v>0.101998</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.298817</v>
+        <v>0.017044</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.668285</v>
+        <v>0.141463</v>
       </c>
     </row>
     <row r="49">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -29034,7 +29034,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -29436,7 +29436,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -32531,7 +32531,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -34719,7 +34719,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E262" s="5" t="n">

--- a/output/pdf_financials_xlsx/ROS.xlsx
+++ b/output/pdf_financials_xlsx/ROS.xlsx
@@ -4509,28 +4509,28 @@
         <v>0</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.028538</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.052241</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.06789000000000001</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.469388</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.076941</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.199094</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.333586</v>
       </c>
     </row>
     <row r="68">
@@ -6649,7 +6649,7 @@
         <v>-0.001103</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000371</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>0</v>
@@ -18527,7 +18527,11 @@
           <t>Shares issued by private placement (note 9)</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -20031,7 +20035,11 @@
           <t>Shares issued by private placement</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -21019,7 +21027,11 @@
           <t>Units issued by private placement</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -24005,7 +24017,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
